--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/3.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/3.xlsx
@@ -426,13 +426,13 @@
         <v>-18.97884214602003</v>
       </c>
       <c r="E2">
-        <v>-12.07281868320261</v>
+        <v>-26.44083347032325</v>
       </c>
       <c r="F2">
-        <v>-0.2364377415589594</v>
+        <v>-2.595653784121438</v>
       </c>
       <c r="G2">
-        <v>-10.67200155179343</v>
+        <v>-16.13364192138962</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.79678020785586</v>
       </c>
       <c r="E3">
-        <v>-12.91114790539858</v>
+        <v>-25.50165966045047</v>
       </c>
       <c r="F3">
-        <v>-0.1156220125954572</v>
+        <v>-2.727234975851723</v>
       </c>
       <c r="G3">
-        <v>-9.893420830776549</v>
+        <v>-15.99500124002325</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.41055669527934</v>
       </c>
       <c r="E4">
-        <v>-13.7016881413916</v>
+        <v>-26.14752420884644</v>
       </c>
       <c r="F4">
-        <v>-0.3235811639660646</v>
+        <v>-2.784842130144609</v>
       </c>
       <c r="G4">
-        <v>-10.26643323886839</v>
+        <v>-15.78460944991149</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.83390816377828</v>
       </c>
       <c r="E5">
-        <v>-13.27434057776176</v>
+        <v>-26.8443340898287</v>
       </c>
       <c r="F5">
-        <v>0.2016128814502527</v>
+        <v>-2.562793277619785</v>
       </c>
       <c r="G5">
-        <v>-10.7432577339807</v>
+        <v>-15.5694057818584</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.08999625421153</v>
       </c>
       <c r="E6">
-        <v>-14.38174266854548</v>
+        <v>-26.63913987559314</v>
       </c>
       <c r="F6">
-        <v>0.03088387463106622</v>
+        <v>-2.759269600052785</v>
       </c>
       <c r="G6">
-        <v>-10.40453595658463</v>
+        <v>-15.47201284263858</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.19320704318775</v>
       </c>
       <c r="E7">
-        <v>-14.7980905688107</v>
+        <v>-28.06409214921673</v>
       </c>
       <c r="F7">
-        <v>0.537520833489869</v>
+        <v>-2.740642930633436</v>
       </c>
       <c r="G7">
-        <v>-9.331286887662761</v>
+        <v>-15.50726353154074</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.18599824805779</v>
       </c>
       <c r="E8">
-        <v>-15.56734244849366</v>
+        <v>-27.59477921695781</v>
       </c>
       <c r="F8">
-        <v>0.4155917787370042</v>
+        <v>-2.327869110553248</v>
       </c>
       <c r="G8">
-        <v>-9.415712420005255</v>
+        <v>-15.0380019777129</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.09785017395365</v>
       </c>
       <c r="E9">
-        <v>-15.37860018032797</v>
+        <v>-28.58207259163609</v>
       </c>
       <c r="F9">
-        <v>0.3717769417007299</v>
+        <v>-2.461703461619147</v>
       </c>
       <c r="G9">
-        <v>-8.981613825622782</v>
+        <v>-15.1024914048179</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.94303875732402</v>
       </c>
       <c r="E10">
-        <v>-16.37548939142851</v>
+        <v>-28.27363822697366</v>
       </c>
       <c r="F10">
-        <v>0.8462011773668684</v>
+        <v>-2.425760600011676</v>
       </c>
       <c r="G10">
-        <v>-7.677219156603463</v>
+        <v>-14.43640136595269</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.75873858232935</v>
       </c>
       <c r="E11">
-        <v>-16.44998731732869</v>
+        <v>-28.98249837729033</v>
       </c>
       <c r="F11">
-        <v>0.6933723617547765</v>
+        <v>-2.44634718670605</v>
       </c>
       <c r="G11">
-        <v>-7.639343205088661</v>
+        <v>-14.18122617105843</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.55891716239936</v>
       </c>
       <c r="E12">
-        <v>-18.50085168287046</v>
+        <v>-29.96233788375199</v>
       </c>
       <c r="F12">
-        <v>0.820516817675667</v>
+        <v>-2.324767702997166</v>
       </c>
       <c r="G12">
-        <v>-7.349895587499103</v>
+        <v>-14.06394347423867</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.343891966142698</v>
       </c>
       <c r="E13">
-        <v>-18.3880564522874</v>
+        <v>-30.21430670601278</v>
       </c>
       <c r="F13">
-        <v>0.6933615929785401</v>
+        <v>-2.253130490003065</v>
       </c>
       <c r="G13">
-        <v>-7.392595003864622</v>
+        <v>-13.70498433196104</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.140830688559808</v>
       </c>
       <c r="E14">
-        <v>-19.39614910808292</v>
+        <v>-30.36178551902058</v>
       </c>
       <c r="F14">
-        <v>0.8548791542785961</v>
+        <v>-2.381066036793629</v>
       </c>
       <c r="G14">
-        <v>-5.917525159568178</v>
+        <v>-13.7737824340854</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.95435326035212</v>
       </c>
       <c r="E15">
-        <v>-20.28096311596762</v>
+        <v>-31.70701853621314</v>
       </c>
       <c r="F15">
-        <v>1.032610350753647</v>
+        <v>-1.840437849928351</v>
       </c>
       <c r="G15">
-        <v>-5.911685357236903</v>
+        <v>-12.51988186090382</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.783320820520254</v>
       </c>
       <c r="E16">
-        <v>-21.29822593162866</v>
+        <v>-31.84398223257513</v>
       </c>
       <c r="F16">
-        <v>1.426494080580395</v>
+        <v>-1.874630371213706</v>
       </c>
       <c r="G16">
-        <v>-5.429736137629804</v>
+        <v>-12.486978348789</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.653345119495699</v>
       </c>
       <c r="E17">
-        <v>-21.14843759687695</v>
+        <v>-33.18716385104222</v>
       </c>
       <c r="F17">
-        <v>1.612306829437158</v>
+        <v>-1.940880710987403</v>
       </c>
       <c r="G17">
-        <v>-4.266430298403145</v>
+        <v>-12.26301332196623</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.570545213006656</v>
       </c>
       <c r="E18">
-        <v>-22.09375654597814</v>
+        <v>-33.32740389834876</v>
       </c>
       <c r="F18">
-        <v>1.392153281529939</v>
+        <v>-1.829098328551429</v>
       </c>
       <c r="G18">
-        <v>-4.055078450084993</v>
+        <v>-12.07408048804002</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.541404055882654</v>
       </c>
       <c r="E19">
-        <v>-23.25745209715122</v>
+        <v>-34.22110277223651</v>
       </c>
       <c r="F19">
-        <v>1.655883925028828</v>
+        <v>-1.723631419194399</v>
       </c>
       <c r="G19">
-        <v>-3.698939892606817</v>
+        <v>-11.53592482626717</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.59445734696436</v>
       </c>
       <c r="E20">
-        <v>-24.82555396263128</v>
+        <v>-35.21941618841247</v>
       </c>
       <c r="F20">
-        <v>1.784343828385365</v>
+        <v>-1.410679184621162</v>
       </c>
       <c r="G20">
-        <v>-3.526960362387218</v>
+        <v>-11.40254956758102</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.7388411622778321</v>
       </c>
       <c r="E21">
-        <v>-24.26829806514339</v>
+        <v>-34.96556125672748</v>
       </c>
       <c r="F21">
-        <v>1.774138341982875</v>
+        <v>-1.371033520723178</v>
       </c>
       <c r="G21">
-        <v>-2.978065290884977</v>
+        <v>-11.40414525053094</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.01888043375711589</v>
       </c>
       <c r="E22">
-        <v>-26.10324026152543</v>
+        <v>-35.89481997276047</v>
       </c>
       <c r="F22">
-        <v>1.860109624515019</v>
+        <v>-1.319661487871164</v>
       </c>
       <c r="G22">
-        <v>-2.275623806725798</v>
+        <v>-11.23070908027407</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.6617424460095408</v>
       </c>
       <c r="E23">
-        <v>-25.42943050002813</v>
+        <v>-36.43613111326734</v>
       </c>
       <c r="F23">
-        <v>1.900746015826751</v>
+        <v>-1.255112614742818</v>
       </c>
       <c r="G23">
-        <v>-2.764713873061106</v>
+        <v>-10.95267953424945</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.191886434419233</v>
       </c>
       <c r="E24">
-        <v>-26.17398861094726</v>
+        <v>-36.59786556245129</v>
       </c>
       <c r="F24">
-        <v>2.069446350876482</v>
+        <v>-1.041368973798461</v>
       </c>
       <c r="G24">
-        <v>-2.160406890322543</v>
+        <v>-10.54347293177676</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.613938932795912</v>
       </c>
       <c r="E25">
-        <v>-26.14862009955629</v>
+        <v>-36.79171594929763</v>
       </c>
       <c r="F25">
-        <v>2.138653133910769</v>
+        <v>-0.952280544729583</v>
       </c>
       <c r="G25">
-        <v>-1.724699370807983</v>
+        <v>-11.3379409608366</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.926656346555015</v>
       </c>
       <c r="E26">
-        <v>-27.69699140378493</v>
+        <v>-36.49981957171122</v>
       </c>
       <c r="F26">
-        <v>2.194090793975723</v>
+        <v>-0.9460628190041699</v>
       </c>
       <c r="G26">
-        <v>-1.795088190063967</v>
+        <v>-10.8708958172473</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.139981307381459</v>
       </c>
       <c r="E27">
-        <v>-26.70643299934712</v>
+        <v>-37.00098126166609</v>
       </c>
       <c r="F27">
-        <v>2.308635781700033</v>
+        <v>-1.030095721813763</v>
       </c>
       <c r="G27">
-        <v>-1.858889023696802</v>
+        <v>-11.08318454995306</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.263208053770395</v>
       </c>
       <c r="E28">
-        <v>-27.08435679765725</v>
+        <v>-37.20003260091025</v>
       </c>
       <c r="F28">
-        <v>2.452428765682388</v>
+        <v>-1.02906523276468</v>
       </c>
       <c r="G28">
-        <v>-2.047646398709427</v>
+        <v>-11.42799773114139</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.302034193024067</v>
       </c>
       <c r="E29">
-        <v>-26.79623716739323</v>
+        <v>-36.85247901353256</v>
       </c>
       <c r="F29">
-        <v>2.147591218186976</v>
+        <v>-0.9773983011172697</v>
       </c>
       <c r="G29">
-        <v>-1.871257221831519</v>
+        <v>-10.8461792842511</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.265694287697675</v>
       </c>
       <c r="E30">
-        <v>-26.12944201213381</v>
+        <v>-36.69902487907164</v>
       </c>
       <c r="F30">
-        <v>2.185477429721414</v>
+        <v>-0.9217543775690185</v>
       </c>
       <c r="G30">
-        <v>-1.940901168341167</v>
+        <v>-10.87475591334609</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.160570355420073</v>
       </c>
       <c r="E31">
-        <v>-25.99336136820332</v>
+        <v>-37.04447725450976</v>
       </c>
       <c r="F31">
-        <v>2.386484093480325</v>
+        <v>-0.88032026844839</v>
       </c>
       <c r="G31">
-        <v>-1.844964869158627</v>
+        <v>-11.12450346882871</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.990423010133745</v>
       </c>
       <c r="E32">
-        <v>-25.48350953662773</v>
+        <v>-36.55053848059713</v>
       </c>
       <c r="F32">
-        <v>2.254483747844224</v>
+        <v>-0.9380723870367659</v>
       </c>
       <c r="G32">
-        <v>-2.621218276661396</v>
+        <v>-11.15390442376297</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.75628910418126</v>
       </c>
       <c r="E33">
-        <v>-25.29538766940108</v>
+        <v>-35.69378063342695</v>
       </c>
       <c r="F33">
-        <v>2.216877524491932</v>
+        <v>-0.916727844168831</v>
       </c>
       <c r="G33">
-        <v>-2.412895577511678</v>
+        <v>-11.14131772962267</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.45938821169557</v>
       </c>
       <c r="E34">
-        <v>-25.72252239475257</v>
+        <v>-35.81225683465262</v>
       </c>
       <c r="F34">
-        <v>2.408787057433299</v>
+        <v>-0.8112833007316763</v>
       </c>
       <c r="G34">
-        <v>-2.979068386183375</v>
+        <v>-11.81653328726688</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.103027962577349</v>
       </c>
       <c r="E35">
-        <v>-24.67500031577227</v>
+        <v>-35.47856717044942</v>
       </c>
       <c r="F35">
-        <v>2.186053973433762</v>
+        <v>-0.7953339147581747</v>
       </c>
       <c r="G35">
-        <v>-3.380240294632258</v>
+        <v>-11.88915341421633</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.6867737761072186</v>
       </c>
       <c r="E36">
-        <v>-24.77368482134742</v>
+        <v>-35.36603685559581</v>
       </c>
       <c r="F36">
-        <v>2.379403208921195</v>
+        <v>-0.9180507469111019</v>
       </c>
       <c r="G36">
-        <v>-3.115264229668992</v>
+        <v>-11.93860303293642</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.2144067517594763</v>
       </c>
       <c r="E37">
-        <v>-23.8619988487012</v>
+        <v>-34.98095353987956</v>
       </c>
       <c r="F37">
-        <v>2.688745418353031</v>
+        <v>-0.5979347910384553</v>
       </c>
       <c r="G37">
-        <v>-3.590688364018188</v>
+        <v>-11.80484375096771</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.3064193357802734</v>
       </c>
       <c r="E38">
-        <v>-23.52354975831593</v>
+        <v>-34.05807544372338</v>
       </c>
       <c r="F38">
-        <v>2.784700184823715</v>
+        <v>-0.9331253769072473</v>
       </c>
       <c r="G38">
-        <v>-3.428534532959146</v>
+        <v>-11.62308817977064</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8737755402764538</v>
       </c>
       <c r="E39">
-        <v>-22.44356757764865</v>
+        <v>-33.74029430870912</v>
       </c>
       <c r="F39">
-        <v>2.667530929167336</v>
+        <v>-0.6590202600556965</v>
       </c>
       <c r="G39">
-        <v>-4.464473753653425</v>
+        <v>-12.03636013216556</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.478885996757639</v>
       </c>
       <c r="E40">
-        <v>-23.04184239269802</v>
+        <v>-33.31840808473252</v>
       </c>
       <c r="F40">
-        <v>2.51527203032837</v>
+        <v>-0.6998968779142408</v>
       </c>
       <c r="G40">
-        <v>-3.94116919916975</v>
+        <v>-11.62814338280911</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.10874593662404</v>
       </c>
       <c r="E41">
-        <v>-22.95028117673693</v>
+        <v>-33.15604870613552</v>
       </c>
       <c r="F41">
-        <v>3.108383090732816</v>
+        <v>-0.7427151889649473</v>
       </c>
       <c r="G41">
-        <v>-3.927582720276581</v>
+        <v>-11.50301800360682</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.757747825350311</v>
       </c>
       <c r="E42">
-        <v>-20.12229897216087</v>
+        <v>-32.54643685640796</v>
       </c>
       <c r="F42">
-        <v>3.273852792911629</v>
+        <v>-0.5446608266296135</v>
       </c>
       <c r="G42">
-        <v>-4.018520095694821</v>
+        <v>-11.83937274094231</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.413024392742826</v>
       </c>
       <c r="E43">
-        <v>-20.13177253978492</v>
+        <v>-31.59828081834096</v>
       </c>
       <c r="F43">
-        <v>2.912668037942988</v>
+        <v>-0.4592710580142348</v>
       </c>
       <c r="G43">
-        <v>-4.086101572333503</v>
+        <v>-12.39795446869246</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.061071843719274</v>
       </c>
       <c r="E44">
-        <v>-19.5777409157905</v>
+        <v>-30.95261099432732</v>
       </c>
       <c r="F44">
-        <v>2.614064783521044</v>
+        <v>-0.5380951865950246</v>
       </c>
       <c r="G44">
-        <v>-5.041462114601922</v>
+        <v>-12.08468747594784</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.697882503643105</v>
       </c>
       <c r="E45">
-        <v>-20.12972566953345</v>
+        <v>-30.88621903690087</v>
       </c>
       <c r="F45">
-        <v>2.988127338133606</v>
+        <v>-0.3948058499935717</v>
       </c>
       <c r="G45">
-        <v>-4.661192990687998</v>
+        <v>-12.1715793647171</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.312835277205101</v>
       </c>
       <c r="E46">
-        <v>-19.25873709279417</v>
+        <v>-30.64380529479627</v>
       </c>
       <c r="F46">
-        <v>2.863885481592125</v>
+        <v>-0.3423055807389447</v>
       </c>
       <c r="G46">
-        <v>-5.550845825092962</v>
+        <v>-12.2047940681126</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.897252867596182</v>
       </c>
       <c r="E47">
-        <v>-17.864143708918</v>
+        <v>-29.64620058480252</v>
       </c>
       <c r="F47">
-        <v>3.035029500480114</v>
+        <v>-0.629162585389191</v>
       </c>
       <c r="G47">
-        <v>-4.596653905399906</v>
+        <v>-12.61776476086345</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.451667711192313</v>
       </c>
       <c r="E48">
-        <v>-17.66623580936078</v>
+        <v>-29.09936017753228</v>
       </c>
       <c r="F48">
-        <v>3.100516913875832</v>
+        <v>-0.4043387020649885</v>
       </c>
       <c r="G48">
-        <v>-5.018129389641138</v>
+        <v>-12.51648524118052</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.969586483652225</v>
       </c>
       <c r="E49">
-        <v>-16.67849864422974</v>
+        <v>-28.71078540835611</v>
       </c>
       <c r="F49">
-        <v>2.820064845984031</v>
+        <v>-0.4296884013254589</v>
       </c>
       <c r="G49">
-        <v>-5.097516271672862</v>
+        <v>-11.81612940071109</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.447528116079503</v>
       </c>
       <c r="E50">
-        <v>-16.11017515626711</v>
+        <v>-28.75579843999235</v>
       </c>
       <c r="F50">
-        <v>3.038076235787611</v>
+        <v>-0.3580826662926641</v>
       </c>
       <c r="G50">
-        <v>-5.189155482745427</v>
+        <v>-12.29452640495455</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.88895191560181</v>
       </c>
       <c r="E51">
-        <v>-16.43607131670312</v>
+        <v>-27.6774917947079</v>
       </c>
       <c r="F51">
-        <v>3.202091324807107</v>
+        <v>-0.4775415294503808</v>
       </c>
       <c r="G51">
-        <v>-5.281152232736234</v>
+        <v>-12.71993812784197</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.289667615263273</v>
       </c>
       <c r="E52">
-        <v>-15.29404451365675</v>
+        <v>-27.78725294770582</v>
       </c>
       <c r="F52">
-        <v>3.042700182630038</v>
+        <v>-0.4194116753263282</v>
       </c>
       <c r="G52">
-        <v>-5.377211022103727</v>
+        <v>-12.96852368184031</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.649455306501338</v>
       </c>
       <c r="E53">
-        <v>-15.53309359957365</v>
+        <v>-26.91472468980393</v>
       </c>
       <c r="F53">
-        <v>3.145207335256865</v>
+        <v>-0.2700918240324949</v>
       </c>
       <c r="G53">
-        <v>-5.222995879247858</v>
+        <v>-12.49012005650577</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.971704215952569</v>
       </c>
       <c r="E54">
-        <v>-14.02816394650059</v>
+        <v>-26.43502343817141</v>
       </c>
       <c r="F54">
-        <v>3.281197098304849</v>
+        <v>-0.3708055612322617</v>
       </c>
       <c r="G54">
-        <v>-6.446470883650771</v>
+        <v>-12.47829478783949</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.252569085846085</v>
       </c>
       <c r="E55">
-        <v>-13.59782306155168</v>
+        <v>-25.70252012506069</v>
       </c>
       <c r="F55">
-        <v>3.234177307787143</v>
+        <v>-0.5290253919017728</v>
       </c>
       <c r="G55">
-        <v>-6.092821856418126</v>
+        <v>-12.85179053558007</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.491810963635288</v>
       </c>
       <c r="E56">
-        <v>-12.48953338986245</v>
+        <v>-26.72375894090047</v>
       </c>
       <c r="F56">
-        <v>3.03060767528397</v>
+        <v>-0.1916504011917986</v>
       </c>
       <c r="G56">
-        <v>-5.762909440702056</v>
+        <v>-12.927317321513</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.688751921266539</v>
       </c>
       <c r="E57">
-        <v>-13.08971922094305</v>
+        <v>-25.84511271461421</v>
       </c>
       <c r="F57">
-        <v>3.022859126598184</v>
+        <v>-0.4110534482320812</v>
       </c>
       <c r="G57">
-        <v>-5.742715112912502</v>
+        <v>-12.91895157293526</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.837419869639717</v>
       </c>
       <c r="E58">
-        <v>-11.67615153097474</v>
+        <v>-25.19425325938778</v>
       </c>
       <c r="F58">
-        <v>3.052741652286773</v>
+        <v>-0.5013595773830749</v>
       </c>
       <c r="G58">
-        <v>-6.223340114303893</v>
+        <v>-13.1312634794598</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.9361476595891</v>
       </c>
       <c r="E59">
-        <v>-10.7805733403738</v>
+        <v>-24.83831520238489</v>
       </c>
       <c r="F59">
-        <v>3.189856338267758</v>
+        <v>-0.4697797268861494</v>
       </c>
       <c r="G59">
-        <v>-6.260931358902317</v>
+        <v>-12.73200506633262</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.980834775372911</v>
       </c>
       <c r="E60">
-        <v>-12.15163224483211</v>
+        <v>-24.28991700005601</v>
       </c>
       <c r="F60">
-        <v>2.997784445315443</v>
+        <v>-0.5097277448861556</v>
       </c>
       <c r="G60">
-        <v>-6.856488569780586</v>
+        <v>-13.51774980789648</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.965811147195058</v>
       </c>
       <c r="E61">
-        <v>-10.87207568617279</v>
+        <v>-24.60201037171664</v>
       </c>
       <c r="F61">
-        <v>2.937475984922028</v>
+        <v>-0.3996981878745056</v>
       </c>
       <c r="G61">
-        <v>-6.330151555582939</v>
+        <v>-13.2552765153609</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.890998028017952</v>
       </c>
       <c r="E62">
-        <v>-10.05867118491504</v>
+        <v>-24.29807278174383</v>
       </c>
       <c r="F62">
-        <v>2.749433271016929</v>
+        <v>-0.7175162525717863</v>
       </c>
       <c r="G62">
-        <v>-6.244428289389051</v>
+        <v>-13.1646801261332</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.753490999903272</v>
       </c>
       <c r="E63">
-        <v>-10.24461032766998</v>
+        <v>-23.8629452997688</v>
       </c>
       <c r="F63">
-        <v>2.247417773898344</v>
+        <v>-0.6643126993921825</v>
       </c>
       <c r="G63">
-        <v>-6.458137246131162</v>
+        <v>-13.10868224833643</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.552569889990602</v>
       </c>
       <c r="E64">
-        <v>-9.96038518505256</v>
+        <v>-23.93145658303085</v>
       </c>
       <c r="F64">
-        <v>2.21598620116652</v>
+        <v>-0.5850395956790754</v>
       </c>
       <c r="G64">
-        <v>-6.230368402483766</v>
+        <v>-13.19610382439197</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.293522272696336</v>
       </c>
       <c r="E65">
-        <v>-8.842458920675011</v>
+        <v>-24.17991130946168</v>
       </c>
       <c r="F65">
-        <v>2.330569293791358</v>
+        <v>-0.5252124167466867</v>
       </c>
       <c r="G65">
-        <v>-5.692106803253663</v>
+        <v>-13.14700843404457</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.97808126907719</v>
       </c>
       <c r="E66">
-        <v>-10.47125139480587</v>
+        <v>-23.35016354551025</v>
       </c>
       <c r="F66">
-        <v>2.107695387333346</v>
+        <v>-0.883274226606773</v>
       </c>
       <c r="G66">
-        <v>-5.651473167304649</v>
+        <v>-13.53840595678876</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.613254952422434</v>
       </c>
       <c r="E67">
-        <v>-9.948593038736588</v>
+        <v>-23.96093694882078</v>
       </c>
       <c r="F67">
-        <v>2.133227327422432</v>
+        <v>-1.013787652754849</v>
       </c>
       <c r="G67">
-        <v>-6.378687463734193</v>
+        <v>-13.67082446781407</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.209634112900551</v>
       </c>
       <c r="E68">
-        <v>-8.725135216084286</v>
+        <v>-23.67015910431426</v>
       </c>
       <c r="F68">
-        <v>1.974593313051521</v>
+        <v>-1.115843345147151</v>
       </c>
       <c r="G68">
-        <v>-6.259332365406849</v>
+        <v>-13.00530715332715</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.771743016943446</v>
       </c>
       <c r="E69">
-        <v>-8.981750252676942</v>
+        <v>-23.58206669944305</v>
       </c>
       <c r="F69">
-        <v>1.943148486441252</v>
+        <v>-1.097224959401829</v>
       </c>
       <c r="G69">
-        <v>-6.122484344449996</v>
+        <v>-13.39005875590125</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.309631340057679</v>
       </c>
       <c r="E70">
-        <v>-9.707764262534671</v>
+        <v>-23.42112020473644</v>
       </c>
       <c r="F70">
-        <v>1.965338792427445</v>
+        <v>-1.321246154712719</v>
       </c>
       <c r="G70">
-        <v>-5.355126372811249</v>
+        <v>-12.77423107468602</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.833297695896637</v>
       </c>
       <c r="E71">
-        <v>-8.589905925267235</v>
+        <v>-23.03866340394463</v>
       </c>
       <c r="F71">
-        <v>1.909248378849085</v>
+        <v>-1.382408661898421</v>
       </c>
       <c r="G71">
-        <v>-5.751249699312743</v>
+        <v>-12.63385732272984</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.343855820116016</v>
       </c>
       <c r="E72">
-        <v>-9.108316572717321</v>
+        <v>-23.42145531181301</v>
       </c>
       <c r="F72">
-        <v>1.338203369320412</v>
+        <v>-1.239386887968072</v>
       </c>
       <c r="G72">
-        <v>-5.520352390130735</v>
+        <v>-13.13000547215488</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.84908566170612</v>
       </c>
       <c r="E73">
-        <v>-9.070404188325105</v>
+        <v>-23.29684076406993</v>
       </c>
       <c r="F73">
-        <v>1.441787399570879</v>
+        <v>-1.459035960126986</v>
       </c>
       <c r="G73">
-        <v>-4.996584359271561</v>
+        <v>-12.99711024257191</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.354154122664547</v>
       </c>
       <c r="E74">
-        <v>-9.18562668097627</v>
+        <v>-23.43576528967724</v>
       </c>
       <c r="F74">
-        <v>1.437957028700334</v>
+        <v>-1.516103018873247</v>
       </c>
       <c r="G74">
-        <v>-4.484171499612088</v>
+        <v>-12.70591134639208</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.854827533047646</v>
       </c>
       <c r="E75">
-        <v>-10.212738927604</v>
+        <v>-23.18174506869098</v>
       </c>
       <c r="F75">
-        <v>1.151302145696371</v>
+        <v>-1.441085238508321</v>
       </c>
       <c r="G75">
-        <v>-4.491689748531773</v>
+        <v>-12.34005633775614</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.354744529309304</v>
       </c>
       <c r="E76">
-        <v>-9.756277804578842</v>
+        <v>-23.60413848175644</v>
       </c>
       <c r="F76">
-        <v>1.229582865260924</v>
+        <v>-1.827450705787261</v>
       </c>
       <c r="G76">
-        <v>-4.678291958398334</v>
+        <v>-12.23451614596418</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.851721581347018</v>
       </c>
       <c r="E77">
-        <v>-10.44742709305152</v>
+        <v>-23.49862050890371</v>
       </c>
       <c r="F77">
-        <v>1.169448362022097</v>
+        <v>-1.727276235766716</v>
       </c>
       <c r="G77">
-        <v>-4.508712573694706</v>
+        <v>-12.40714123256394</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.335140209340482</v>
       </c>
       <c r="E78">
-        <v>-11.02966658163972</v>
+        <v>-24.27678895390778</v>
       </c>
       <c r="F78">
-        <v>0.8840840754316954</v>
+        <v>-1.678701599633956</v>
       </c>
       <c r="G78">
-        <v>-3.976876743356329</v>
+        <v>-11.99921912176048</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.805085406413157</v>
       </c>
       <c r="E79">
-        <v>-10.89946842544519</v>
+        <v>-24.44685126679183</v>
       </c>
       <c r="F79">
-        <v>1.123526986680504</v>
+        <v>-2.032456727366888</v>
       </c>
       <c r="G79">
-        <v>-3.243968308599238</v>
+        <v>-12.40105644986276</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.25482465461036</v>
       </c>
       <c r="E80">
-        <v>-11.88466964513193</v>
+        <v>-24.66003370917692</v>
       </c>
       <c r="F80">
-        <v>1.297560351069457</v>
+        <v>-1.913548728532033</v>
       </c>
       <c r="G80">
-        <v>-3.16678293935113</v>
+        <v>-12.02864656105906</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.672575834334695</v>
       </c>
       <c r="E81">
-        <v>-12.12418063539761</v>
+        <v>-25.52896183024271</v>
       </c>
       <c r="F81">
-        <v>1.322769227871452</v>
+        <v>-1.925922052427649</v>
       </c>
       <c r="G81">
-        <v>-2.986288686004526</v>
+        <v>-11.57172175518331</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.061272800474251</v>
       </c>
       <c r="E82">
-        <v>-13.08007809978072</v>
+        <v>-24.87117380978455</v>
       </c>
       <c r="F82">
-        <v>1.129209587063708</v>
+        <v>-1.985668879721966</v>
       </c>
       <c r="G82">
-        <v>-3.511486872536664</v>
+        <v>-11.84650034548836</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.4170255757084153</v>
       </c>
       <c r="E83">
-        <v>-13.70415163125178</v>
+        <v>-26.24758989899393</v>
       </c>
       <c r="F83">
-        <v>1.164542770262718</v>
+        <v>-2.09334421657486</v>
       </c>
       <c r="G83">
-        <v>-2.53271415221452</v>
+        <v>-11.94576043239233</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2653177402463416</v>
       </c>
       <c r="E84">
-        <v>-15.07934956095309</v>
+        <v>-26.95714290583377</v>
       </c>
       <c r="F84">
-        <v>1.209269639809475</v>
+        <v>-1.945799556625226</v>
       </c>
       <c r="G84">
-        <v>-2.239853362173973</v>
+        <v>-11.61071998163593</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.9744335900084287</v>
       </c>
       <c r="E85">
-        <v>-15.81629077859133</v>
+        <v>-27.53263949662455</v>
       </c>
       <c r="F85">
-        <v>0.8823229663333436</v>
+        <v>-2.098818896739962</v>
       </c>
       <c r="G85">
-        <v>-1.965184019871721</v>
+        <v>-11.56307461023474</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.706976977043323</v>
       </c>
       <c r="E86">
-        <v>-17.58292094456766</v>
+        <v>-28.16901236350045</v>
       </c>
       <c r="F86">
-        <v>0.8460586981735869</v>
+        <v>-2.27870053499268</v>
       </c>
       <c r="G86">
-        <v>-1.869757544702229</v>
+        <v>-11.59856696896126</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.45825374840776</v>
       </c>
       <c r="E87">
-        <v>-18.22503138801127</v>
+        <v>-28.78808645966704</v>
       </c>
       <c r="F87">
-        <v>0.90514448828047</v>
+        <v>-2.308896183559528</v>
       </c>
       <c r="G87">
-        <v>-1.409134859459115</v>
+        <v>-11.5057227193124</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.207964246398626</v>
       </c>
       <c r="E88">
-        <v>-19.39202819673594</v>
+        <v>-29.56705870880747</v>
       </c>
       <c r="F88">
-        <v>1.010933632557189</v>
+        <v>-2.201176114866883</v>
       </c>
       <c r="G88">
-        <v>-1.258978445434392</v>
+        <v>-11.48562439734349</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.944169267982635</v>
       </c>
       <c r="E89">
-        <v>-20.05827993511444</v>
+        <v>-31.23210388160673</v>
       </c>
       <c r="F89">
-        <v>0.9346708159858557</v>
+        <v>-2.18609320119671</v>
       </c>
       <c r="G89">
-        <v>-1.201394816324308</v>
+        <v>-11.39926550640606</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.651237358560738</v>
       </c>
       <c r="E90">
-        <v>-23.14692563204601</v>
+        <v>-32.24095958527253</v>
       </c>
       <c r="F90">
-        <v>1.287258774048243</v>
+        <v>-2.401207790192699</v>
       </c>
       <c r="G90">
-        <v>-1.518647705898206</v>
+        <v>-11.87770885828707</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.301354238413342</v>
       </c>
       <c r="E91">
-        <v>-24.11635870523804</v>
+        <v>-33.20599551020312</v>
       </c>
       <c r="F91">
-        <v>1.044671380138408</v>
+        <v>-2.294544718306026</v>
       </c>
       <c r="G91">
-        <v>-1.690220039016474</v>
+        <v>-10.96856022120134</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.874756961497098</v>
       </c>
       <c r="E92">
-        <v>-26.17167456072934</v>
+        <v>-35.03814590235942</v>
       </c>
       <c r="F92">
-        <v>0.7336028530391372</v>
+        <v>-2.778355185013286</v>
       </c>
       <c r="G92">
-        <v>-1.439191302410158</v>
+        <v>-11.64969172372423</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.349251728826284</v>
       </c>
       <c r="E93">
-        <v>-27.05472246375106</v>
+        <v>-35.89068774022847</v>
       </c>
       <c r="F93">
-        <v>0.9827210955526438</v>
+        <v>-2.556917667631728</v>
       </c>
       <c r="G93">
-        <v>-1.718018689909734</v>
+        <v>-11.89470188854015</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.698541173252997</v>
       </c>
       <c r="E94">
-        <v>-30.39494753417875</v>
+        <v>-36.99364060529966</v>
       </c>
       <c r="F94">
-        <v>1.070879268028178</v>
+        <v>-2.704827637605996</v>
       </c>
       <c r="G94">
-        <v>-1.742698806905001</v>
+        <v>-11.35348728268902</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.911682331831522</v>
       </c>
       <c r="E95">
-        <v>-31.46588635225271</v>
+        <v>-38.56480824768291</v>
       </c>
       <c r="F95">
-        <v>0.9125020475521353</v>
+        <v>-2.687208262948451</v>
       </c>
       <c r="G95">
-        <v>-2.269390049475351</v>
+        <v>-11.57445957634429</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.97014515469385</v>
       </c>
       <c r="E96">
-        <v>-33.070134497262</v>
+        <v>-41.14826191279278</v>
       </c>
       <c r="F96">
-        <v>0.7012749867774837</v>
+        <v>-3.119889408452717</v>
       </c>
       <c r="G96">
-        <v>-1.98581202912692</v>
+        <v>-11.37856135460346</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.878541468285635</v>
       </c>
       <c r="E97">
-        <v>-35.72913443000483</v>
+        <v>-41.94467105109975</v>
       </c>
       <c r="F97">
-        <v>1.122216509449275</v>
+        <v>-2.998251939025637</v>
       </c>
       <c r="G97">
-        <v>-1.920835951827644</v>
+        <v>-11.9530668063975</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>6.618168277276033</v>
       </c>
       <c r="E98">
-        <v>-38.45336023811714</v>
+        <v>-43.5619498800661</v>
       </c>
       <c r="F98">
-        <v>0.7644910167547252</v>
+        <v>-2.81133414805354</v>
       </c>
       <c r="G98">
-        <v>-2.937504486937826</v>
+        <v>-12.21070670244574</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>6.230120859925466</v>
       </c>
       <c r="E99">
-        <v>-40.72256497793873</v>
+        <v>-45.1839156796304</v>
       </c>
       <c r="F99">
-        <v>0.6084870688877027</v>
+        <v>-3.322508075177476</v>
       </c>
       <c r="G99">
-        <v>-2.857776618715558</v>
+        <v>-12.20105646219877</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.666596493439896</v>
       </c>
       <c r="E100">
-        <v>-43.11985081235627</v>
+        <v>-46.84584752654938</v>
       </c>
       <c r="F100">
-        <v>0.7625244725404792</v>
+        <v>-3.337084027997136</v>
       </c>
       <c r="G100">
-        <v>-2.477156576974471</v>
+        <v>-12.60519792999637</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.034484118742367</v>
       </c>
       <c r="E101">
-        <v>-45.32024538963131</v>
+        <v>-49.24864904230827</v>
       </c>
       <c r="F101">
-        <v>0.6038067930618854</v>
+        <v>-3.570685292321402</v>
       </c>
       <c r="G101">
-        <v>-2.947462607919954</v>
+        <v>-13.18338801897563</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>4.19423948211647</v>
       </c>
       <c r="E102">
-        <v>-47.20768618518427</v>
+        <v>-50.93160546192637</v>
       </c>
       <c r="F102">
-        <v>0.761760717795098</v>
+        <v>-3.490764405299306</v>
       </c>
       <c r="G102">
-        <v>-3.898936569725267</v>
+        <v>-12.57886916132255</v>
       </c>
     </row>
   </sheetData>
